--- a/resources/tenable/TenableWAS_bWAAP.xlsx
+++ b/resources/tenable/TenableWAS_bWAAP.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vulnerabilities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,98 +413,103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>solution</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>references</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>cvss</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>plugin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cvss</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>plugin_details</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>instances</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>detection_method</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>detection_result</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>insight</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>log_method</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>plugin_details</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>port</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>product_detection_result</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>protocol</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>references</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>solution</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>instances</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
         </is>
       </c>
     </row>
@@ -533,43 +526,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>['The only proven method to prevent against SQL injection attacks while still maintaining full application functionality is to use parameterized queries (also known as prepared statements). When utilising this method of querying the database, any value supplied by the client will be handled as a string value rather than part of the SQL query.', 'Additionally, when utilising parameterized queries, the database engine will automatically check to make sure the string being used matches that of the column. For example, the database engine will check that the user supplied input is an integer if the database column is configured to contain integers.']</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>['CWE 89', 'WASC SQL Injection', 'OWASP 2013-A1', 'OWASP 2021-A3', 'OWASP 2010-A1', 'OWASP 2017-A1', 'OWASP 2019-API8']</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 7.2', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:L/VA:L/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 8.6', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:L/A:L', 'CVSS BASE SCORE 9.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:C/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>98115</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>['7.2', '8.6', '9.0', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:L/VA:L/SC:N/SI:N/SA:N', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:L/A:L', 'CVSS2#AV:N/AC:L/Au:N/C:C/I:P/A:P']</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2025-01-07T00:00:00+00:00",
@@ -579,21 +570,19 @@
 </t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search', 'input_type': 'link', 'input_name': 'q', 'payload': '"\'`--', 'proof': 'SQLITE_ERROR: near &amp;quot;`--%&amp;#39; OR description LIKE &amp;#39;%nessus_was_textjvihbcaq&amp;quot;&amp;#39;`&amp;quot;: syntax error', 'output': "The scanner was able to detect a possible SQL injection. The detected database engine used is 'sqlite'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>['CWE 89', 'WASC SQL Injection', 'OWASP 2013-A1, 2021-A3, 2010-A1, 2017-A1, 2019-API8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>['The only proven method to prevent against SQL injection attacks while still maintaining full application functionality is to use parameterized queries (also known as prepared statements). When utilising this method of querying the database, any value supplied by the client will be handled as a string value rather than part of the SQL query.', 'Additionally, when utilising parameterized queries, the database engine will automatically check to make sure the string being used matches that of the column. For example, the database engine will check that the user supplied input is an integer if the database column is configured to contain integers.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -603,7 +592,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -620,43 +614,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>['The only proven method to prevent against SQL injection attacks while still maintaining full application functionality is to use parameterized queries (also known as prepared statements). When utilising this method of querying the database, any value supplied by the client will be handled as a string value rather than part of the SQL query.', 'Additionally, when utilising parameterized queries, the database engine will automatically check to make sure the string being used matches that of the column. For example, the database engine will check that the user supplied input is an integer if the database column is configured to contain integers.']</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['CWE 89', 'WASC SQL Injection', 'OWASP 2013-A1', 'OWASP 2021-A3', 'OWASP 2010-A1', 'OWASP 2017-A1', 'OWASP 2019-API8']</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 7.2', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:L/VA:L/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 8.6', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:L/A:L', 'CVSS BASE SCORE 9.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:C/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>98117</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['7.2', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:L/VA:L/SC:N/SI:N/SA:N', '8.6', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:L/A:L', '9.0', 'CVSS2#AV:N/AC:L/Au:N/C:C/I:P/A:P']</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2025-03-18T00:00:00+00:00",
@@ -666,31 +658,34 @@
 </t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search', 'input_type': 'link', 'input_name': 'q', 'payload': "10002'+(select '1')+'1", 'proof': "10002'+(select '1','2')+'1 for TRUE statement and 10002'+(select '1')+'1 for FALSE statement", 'output': 'A differential based SQL Injection has been identified by the scanner.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>['CWE 89', 'WASC SQL Injection', 'OWASP 2013-A1, 2021-A3, 2010-A1, 2017-A1, 2019-API8', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>['The only proven method to prevent against SQL injection attacks while still maintaining full application functionality is to use parameterized queries (also known as prepared statements). When utilising this method of querying the database, any value supplied by the client will be handled as a string value rather than part of the SQL query.', 'Additionally, when utilising parameterized queries, the database engine will automatically check to make sure the string being used matches that of the column. For example, the database engine will check that the user supplied input is an integer if the database column is configured to contain integers.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[{'instance': 'application/json;', 'input_type': 'link', 'input_name': 'q', 'payload': "10002'+(select '1')+'1", 'proof': "10002'+(select '1','2')+'1 for TRUE statement and 10002'+(select '1')+'1 for FALSE statement", 'output': 'A differential based SQL Injection has been identified by the scanner.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -707,43 +702,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>['Remove the secret exposure by identifying the root cause of the issue (for example manual data insertion in the code, environment variables being bundled in front-end JavaScript). Rotate the secrets to avoid further reuse in case it has been previously retrieved by a malicious actor.']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>['CWE 16', 'CWE 200', 'WASC Application Misconfiguration', 'WASC Information Leakage', 'OWASP 2021-A5', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2023-API3', 'OWASP 2019-API3', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 8.7', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:H/VI:N/VA:N/SC:L/SI:L/SA:L', 'CVSSV3 BASE SCORE 8.6', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:H/I:N/A:N', 'CVSS BASE SCORE 7.8', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:C/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>114129</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>['8.7', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:H/VI:N/VA:N/SC:L/SI:L/SA:L', '8.6', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:H/I:N/A:N', '7.8', 'CVSS2#AV:N/AC:L/Au:N/C:C/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2023-12-11T00:00:00+00:00",
 "modification_date": "2025-04-02T00:00:00+00:00",
@@ -753,21 +746,19 @@
 </t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - "password":"9283f1b2e9669749081963be0462e466" - "password":"6edd9d726cbdc873c539e41ae8757b8c" - "password":"2c17c6393771ee3048ae34d6b380c5ec" - "password":"00479e957b6b42c459ee5746478e4d45" - "password":"402f1c4a75e316afec5a6ea63147f739"', 'output': 'The scanner identified one or more `Generic Password` secret(s) on the target page.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['CWE 16, 200', 'WASC Application Misconfiguration, Information Leakage', 'OWASP 2021-A5, 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2023-API3, 2019-API3, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>['Remove the secret exposure by identifying the root cause of the issue (for example manual data insertion in the code, environment variables being bundled in front-end JavaScript). Rotate the secrets to avoid further reuse in case it has been previously retrieved by a malicious actor.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -777,7 +768,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -794,43 +790,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>['The application should ensure that the supplied value for a redirect is permitted. This can be achieved by performing whitelisting on the parameter value.', 'The whitelist should contain a list of pages or sites that the application is permitted to redirect users to. If the supplied value does not match any value in the whitelist then the server should redirect to a standard error page.']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>['CWE 601', 'WASC URL Redirector Abuse', 'OWASP 2021-A1', 'OWASP 2013-A10', 'OWASP 2010-A10', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 5.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:A/VC:N/VI:L/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 4.7', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:N/I:L/A:N', 'CVSS BASE SCORE 4.3', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:N/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>98054</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>['5.1', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:A/VC:N/VI:L/VA:N/SC:N/SI:N/SA:N', '4.7', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:N/I:L/A:N', '4.3', 'CVSS2#AV:N/AC:M/Au:N/C:N/I:P/A:N']</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2023-07-13T00:00:00+00:00",
@@ -840,21 +834,19 @@
 </t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect', 'input_type': 'link', 'input_name': 'to', 'payload': 'https://98147a45-d7d1-4fb3-a532-d4d4b2db551e.com?x=https://github.com/juice-shop/juice-shop', 'proof': 'The issue was raised because the scanner was redirected to https://98147a45-d7d1-4fb3-a532-d4d4b2db551e.com? x=https://github.com/juice-shop/juice-shop', 'output': "An unvalidated redirect was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect?to=https%3A%2F% 2F98147a45-d7d1-4fb3-a532-d4d4b2db551e.com%3Fx%3Dhttps%3A%2F%2Fgithub.com%2Fjuice-shop%2Fjuice-shop by injecting https://98147a45-d7d1-4fb3-a532-d4d4b2db551e.com?x=https://github.com/juice-shop/juice-shop into the query parameter 'to' to create the url 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect?to=https%3A%2F%2F98147a45-d7d14fb3-a532-d4d4b2db551e.com%3Fx%3Dhttps%3A%2F%2Fgithub.com%2Fjuice-shop%2Fjuice-shop'.", 'request_method': '', 'http_status_code': 302, 'http_protocol': '', 'response_content_type': 'text/plain'}]</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>['CWE 601', 'WASC URL Redirector Abuse', 'OWASP 2021-A1, 2013-A10, 2010-A10, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>['The application should ensure that the supplied value for a redirect is permitted. This can be achieved by performing whitelisting on the parameter value.', 'The whitelist should contain a list of pages or sites that the application is permitted to redirect users to. If the supplied value does not match any value in the whitelist then the server should redirect to a standard error page.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -864,7 +856,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -881,43 +878,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>['Depending on the framework being used the implementation methods will vary, however it is advised that the `Strict-Transport-Security` header be configured on the server.', ""One of the options for this header is `max-age`, which is a representation (in milliseconds) determining the time in which the client's browser will adhere to the header policy."", 'Depending on the environment and the application this time period could be from as low as minutes to as long as days.']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>['CWE 319', 'CWE 523', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A2', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.3', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:N/VC:L/VI:L/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 6.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:L/A:N', 'CVSS BASE SCORE 5.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>98056</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>['6.3', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:N/VC:L/VI:L/VA:N/SC:N/SI:N/SA:N', '6.5', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:L/A:N', '5.8', 'CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2024-03-18T00:00:00+00:00",
@@ -927,21 +922,19 @@
 </t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>['CWE 319, 523', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9, 2013-A6, 2017-A3, 2021-A2, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>['Depending on the framework being used the implementation methods will vary, however it is advised that the `Strict-Transport-Security` header be configured on the server.', ""One of the options for this header is `max-age`, which is a representation (in milliseconds) determining the time in which the client's browser will adhere to the header policy."", 'Depending on the environment and the application this time period could be from as low as minutes to as long as days.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -951,7 +944,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -968,43 +966,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>['Unless the web server is being utilised to share static and non-sensitive files, enabling directory listing is considered a poor security practice', 'This can typically be done with a simple configuration change on the server. The steps to disable the directory listing will differ depending on the type of server being used (IIS, Apache, etc.). If directory listing is required, and permitted, then steps should be taken to ensure that the risk of such a configuration is reduced.', 'These can include:', '1. Requiring authentication to access affected pages. 2. Adding the affected path to the `robots.txt` file to prevent the directory contents being searchable via search engines. 3. Ensuring that sensitive files are not stored within the web or document root. 4. Removing any files that are not required for the application to function.']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>['CWE 548', 'WASC Directory Indexing', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.9', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 5.3', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>98084</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>['6.9', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '5.3', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2019-02-04T00:00:00+00:00",
 "modification_date": "2024-08-12T00:00:00+00:00",
@@ -1014,21 +1010,19 @@
 </t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/juicy_malware_linux_amd_64.url', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>['CWE 548', 'WASC Directory Indexing', 'OWASP 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2019-API7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>['Unless the web server is being utilised to share static and non-sensitive files, enabling directory listing is considered a poor security practice', 'This can typically be done with a simple configuration change on the server. The steps to disable the directory listing will differ depending on the type of server being used (IIS, Apache, etc.). If directory listing is required, and permitted, then steps should be taken to ensure that the risk of such a configuration is reduced.', 'These can include:', '1. Requiring authentication to access affected pages. 2. Adding the affected path to the `robots.txt` file to prevent the directory contents being searchable via search engines. 3. Ensuring that sensitive files are not stored within the web or document root. 4. Removing any files that are not required for the application to function.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1038,7 +1032,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1055,43 +1054,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>['Client-side document rewriting, redirection, or other sensitive action, using untrusted data, should be avoided wherever possible, as these may not be inspected by server side filtering.', 'To remedy DOM XSS vulnerabilities where these sensitive document actions must be used, it is essential to:', '1. Ensure any untrusted data is treated as text, as opposed to being interpreted as code or mark-up within the page.', '2. Escape untrusted data prior to being used within the page. Escaping methods will vary depending on where the untrusted data is being used. (See references for details.)', '3. Use `document.createElement`, `element.setAttribute`, `element.appendChild`, etc. to build dynamic interfaces as opposed to HTML rendering methods such as `document.write`, `document.writeIn`, `element.innerHTML`, or `element.outerHTML `etc.']</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>['CWE 79', 'WASC Cross-Site Scripting', 'OWASP 2021-A3', 'OWASP 2010-A2', 'OWASP 2013-A3', 'OWASP 2017-A7', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 5.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:A/VC:N/VI:N/VA:N/SC:L/SI:L/SA:N', 'CVSSV3 BASE SCORE 6.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:L/I:L/A:N', 'CVSS BASE SCORE 5.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>98109</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>['5.1', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:A/VC:N/VI:N/VA:N/SC:L/SI:L/SA:N', '6.1', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:L/I:L/A:N', '5.8', 'CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2025-01-17T00:00:00+00:00",
@@ -1101,21 +1098,19 @@
 </t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'ui_input_dom', 'input_name': 'mat-input-0', 'payload': 'javascript:window.top._tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()//"//`//\'//"//--&gt;&lt;/style&gt;&lt;', 'proof': '', 'output': 'Vulnerability has been detected on URL \'https://juice-shop-16-0-1-178712031365.us-west1.run.app/\' by exploiting \'ui_input_dom\' element named \'mat-input-0\' and injecting following payload: | javascript:window.top._tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()//"//`//\'//"//--&gt;&lt;/style&gt;&lt; /select&gt;&lt;/noscript&gt;&lt;/noembed&gt;&lt;/template&gt;&lt;/title&gt;&lt;/textarea&gt;&lt;/script&gt;&lt;iframe/srcdoc="&lt;svg/onload=window.top. _tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()&gt;"&gt;&lt;frame/onload=window.top. _tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()&gt;*/ window.top. _tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink()//', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>['CWE 79', 'WASC Cross-Site Scripting', 'OWASP 2021-A3, 2010-A2, 2013-A3, 2017-A7, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>['Client-side document rewriting, redirection, or other sensitive action, using untrusted data, should be avoided wherever possible, as these may not be inspected by server side filtering.', 'To remedy DOM XSS vulnerabilities where these sensitive document actions must be used, it is essential to:', '1. Ensure any untrusted data is treated as text, as opposed to being interpreted as code or mark-up within the page.', '2. Escape untrusted data prior to being used within the page. Escaping methods will vary depending on where the untrusted data is being used. (See references for details.)', '3. Use `document.createElement`, `element.setAttribute`, `element.appendChild`, etc. to build dynamic interfaces as opposed to HTML rendering methods such as `document.write`, `document.writeIn`, `element.innerHTML`, or `element.outerHTML `etc.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1125,7 +1120,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1142,43 +1142,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>['Upgrade to jQuery version 3.4.0 or later.']</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>['CWE 1321', 'CWE 20', 'CWE 400', 'CWE 79', 'WASC Cross-Site Scripting', 'WASC Denial of Service', 'WASC Improper Input Handling', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2010-A2', 'OWASP 2013-A3', 'OWASP 2013-A9', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2013-A4', 'OWASP 2017-A7', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2019-11358', 'BID 108023']</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 6.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:L/I:L/A:N', 'CVSS BASE SCORE 4.3', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:N/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>98590</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>['6.1', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:L/I:L/A:N', '4.3', 'CVSS2#AV:N/AC:M/Au:N/C:N/I:P/A:N']</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2019-04-25T00:00:00+00:00",
 "modification_date": "2023-03-14T00:00:00+00:00",
@@ -1188,21 +1186,19 @@
 </t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.2.4 Fixed Version: 3.4.0 Detected technology URL: https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>['CWE 1321, 20, 400, 79', 'WASC Cross-Site Scripting, Denial of Service, Improper Input Handling', 'OWASP 2010-A4, 2021-A3, 2021-A6, 2010-A2, 2013-A3, 2013-A9, 2017-A9, 2017-A5, 2013-A4, 2017-A7, 2019-API7, 2023-API8', 'CVE CVE-2019-11358', 'BID 108023']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>['Upgrade to jQuery version 3.4.0 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1212,7 +1208,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1229,43 +1230,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>['Reconfigure the server to disable cipher suites without forward secrecy and retain only cipher suites that provide forward secrecy (ECDHE or DHE based cipher suites).']</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>['CWE 327', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A2', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.0', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:P/VC:H/VI:L/VA:N/SC:L/SI:L/SA:L', 'CVSSV3 BASE SCORE 6.5', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:L/A:N', 'CVSS BASE SCORE 5.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>98617</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>['6.0', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:P/VC:H/VI:L/VA:N/SC:L/SI:L/SA:L', '6.5', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:L/A:N', '5.8', 'CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:N']</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2019-06-12T00:00:00+00:00",
 "modification_date": "2022-11-10T00:00:00+00:00",
@@ -1275,21 +1274,19 @@
 </t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength -------------------------------------------------------------------- TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['CWE 327', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9, 2013-A6, 2017-A3, 2021-A2, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>['Reconfigure the server to disable cipher suites without forward secrecy and retain only cipher suites that provide forward secrecy (ECDHE or DHE based cipher suites).']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1299,7 +1296,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1316,43 +1318,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>['It is important that the server does not deliver server side code to the client, and the server misconfiguration or server code should be changed to prevent this.']</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>['CWE 540', 'WASC Information Leakage', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2010-A6', 'OWASP 2013-A5', 'OWASP 2023-API3', 'OWASP 2019-API3']</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.9', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 5.3', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>98779</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>['6.9', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '5.3', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2019-12-19T00:00:00+00:00",
 "modification_date": "2024-01-03T00:00:00+00:00",
@@ -1362,21 +1362,19 @@
 </t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/swagger-ui-bundle.js', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - &lt;?php', 'output': "The scanner detected the presence of a 'PHP' source code in the web application response.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>['CWE 540', 'WASC Information Leakage', 'OWASP 2017-A6, 2021-A1, 2010-A6, 2013-A5, 2023-API3, 2019-API3', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>['It is important that the server does not deliver server side code to the client, and the server misconfiguration or server code should be changed to prevent this.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1386,7 +1384,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1406,43 +1409,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>[Upgrade to jQuery version 3.5.0 or later.]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>['CWE 79', 'WASC Cross-Site Scripting', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2010-A2', 'OWASP 2013-A3', 'OWASP 2013-A9', 'OWASP 2017-A7', 'OWASP 2017-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2020-11022', 'CVE-2020-11023']</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 6.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:L/I:L/A:N', 'CVSS BASE SCORE 4.3', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:N/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>112383</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>['6.1', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:L/I:L/A:N', '4.3', 'CVSS2#AV:N/AC:M/Au:N/C:N/I:P/A:N']</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2020-05-14T00:00:00+00:00",
 "modification_date": "2023-03-14T00:00:00+00:00",
@@ -1452,21 +1453,19 @@
 </t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.2.4 Fixed Version: 3.5.0 Detected technology URL: https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['CWE 79', 'WASC Cross-Site Scripting', 'OWASP 2021-A3, 2021-A6, 2010-A2, 2013-A3, 2013-A9, 2017-A7, 2017-A9, 2019-API7, 2023-API8', 'CVE CVE-2020-11022, CVE-2020-11023', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[Upgrade to jQuery version 3.5.0 or later.]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1476,7 +1475,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1493,43 +1497,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>['Upgrade to jQuery version 3.0.0 or later.']</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>['CWE 79', 'WASC Cross-Site Scripting', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2010-A2', 'OWASP 2013-A3', 'OWASP 2013-A9', 'OWASP 2017-A7', 'OWASP 2017-A9', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2015-9251', 'BID 105658']</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>['CVSSV3 BASE SCORE 6.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:L/I:L/A:N', 'CVSS BASE SCORE 4.3', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:N/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>112435</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>['6.1', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:C/C:L/I:L/A:N', '4.3', 'CVSS2#AV:N/AC:M/Au:N/C:N/I:P/A:N']</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2018-11-05T00:00:00+00:00",
 "modification_date": "2023-03-14T00:00:00+00:00",
@@ -1539,21 +1541,19 @@
 </t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.2.4 Fixed Version: 3.0.0 Detected technology URL: https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>['CWE 79', 'WASC Cross-Site Scripting', 'OWASP 2021-A3, 2021-A6, 2010-A2, 2013-A3, 2013-A9, 2017-A7, 2017-A9, 2019-API7, 2023-API8', 'CVE CVE-2015-9251', 'BID 105658']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>['Upgrade to jQuery version 3.0.0 or later.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1563,7 +1563,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1580,43 +1585,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>['Ensure that the missing properties are declared in the OpenAPI definition file according to the file specification and that the API backend enforces the validation of these properties on the inputs.']</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>['CWE 20', 'WASC Improper Input Handling', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2013-A4', 'OWASP 2017-A5', 'OWASP 2019-API7', 'OWASP 2023-API8']</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.3', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:N/VC:L/VI:L/VA:L/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 5.6', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:L/A:L', 'CVSS BASE SCORE 6.8', 'CVSS VECTOR CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:P']</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
         <v>113258</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>['6.3', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:N/VC:L/VI:L/VA:L/SC:N/SI:N/SA:N', '5.6', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:L/A:L', '6.8', 'CVSS2#AV:N/AC:M/Au:N/C:P/I:P/A:P']</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2022-06-28T00:00:00+00:00",
 "modification_date": "2023-10-05T00:00:00+00:00",
@@ -1626,21 +1629,19 @@
 </t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The scanner detected the presence of permissive input(s) in the API host(s) used in the detected OpenAPI file on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/. The following components have parameter with permissive inputs : - Component 'Order' has parameter 'cid' (String) without the 'format' property declared - Component 'Order' has parameter 'cid' (String) without the 'maxLength' property declared - Component 'Order' has parameter 'cid' (String) without the 'pattern' property declared - Component 'OrderConfirmation' has parameter 'cid' (String) without the 'format' property declared - Component 'OrderConfirmation' has parameter 'cid' (String) without the 'maxLength' property declared - Component 'OrderConfirmation' has parameter 'cid' (String) without the 'pattern' property declared - Component 'OrderConfirmation' has parameter 'orderNo' (String) without the 'format' property declared - Component 'OrderConfirmation' has parameter 'orderNo' (String) without the 'maxLength' property declared - Component 'OrderConfirmation' has parameter 'orderNo' (String) without the 'pattern' property declared - Component 'OrderConfirmation' has parameter 'paymentDue' (String) without the 'maxLength' property declared - Component 'OrderConfirmation' has parameter 'paymentDue' (String) without the 'pattern' property declared - Component 'OrderLine' has parameter 'productId' (Integer) without the 'format' property declared - Component 'OrderLine' has parameter 'productId' (Integer) without the 'maximum' property declared - Component 'OrderLine' has parameter 'productId' (Integer) without the 'minimum' property declared - Component 'OrderLine' has parameter 'quantity' (Integer) without the 'format' property declared - Component 'OrderLine' has parameter 'quantity' (Integer) without the 'maximum' property declared - Component 'OrderLine' has parameter 'customerReference' (String) without the 'format' property declared - Component 'OrderLine' has parameter 'customerReference' (String) without the 'maxLength' property declared - Component 'OrderLine' has parameter 'customerReference' (String) without the 'pattern' property declared", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>['CWE 20', 'WASC Improper Input Handling', 'OWASP 2010-A4, 2021-A3, 2013-A4, 2017-A5, 2019-API7, 2023-API8', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>['Ensure that the missing properties are declared in the OpenAPI definition file according to the file specification and that the API backend enforces the validation of these properties on the inputs.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1650,7 +1651,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1667,43 +1673,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>['Ensure that the detected sensitive endpoint is not publicly available by requiring authentication or applying IP source filtering.']</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>['CWE 16', 'CWE 538', 'WASC Application Misconfiguration', 'WASC Predictable Resource Location', 'OWASP 2021-A5', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2023-API3', 'OWASP 2019-API3', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 6.9', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 5.3', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 5.0', 'CVSS VECTOR CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
         <v>114012</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>['6.9', 'CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '5.3', 'CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:N', '5.0', 'CVSS2#AV:N/AC:L/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2023-09-11T00:00:00+00:00",
 "modification_date": "2023-10-30T00:00:00+00:00",
@@ -1713,21 +1717,19 @@
 </t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/metrics', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '# HELP file_uploads_count Total number of successful file uploads grouped by file type. # TYPE file_uploads_count counter # HELP file_upload_errors Total number of failed file uploads grouped by file type.', 'output': 'The scanner was able to detect the exposure of a sensitive Prometheus endpoint at the following URL : https://juice\ufffeshop-16-0-1-178712031365.us-west1.run.app/metrics', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>['CWE 16, 538', 'WASC Application Misconfiguration, Predictable Resource Location', 'OWASP 2021-A5, 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2023-API3, 2019-API3, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>['Ensure that the detected sensitive endpoint is not publicly available by requiring authentication or applying IP source filtering.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1737,7 +1739,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1754,43 +1761,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>[""Unless the target application is specifically designed to serve public content to any domain, the 'Access-Control-Allow-Origin' should be configured with an allowlist including only known and trusted domains to perform cross-domain requests if needed, or should be disabled.""]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>['CWE 16', 'WASC Application Misconfiguration', 'OWASP 2021-A5', 'OWASP 2017-A6', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
         <v>98057</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2024-03-25T00:00:00+00:00",
@@ -1800,21 +1805,19 @@
 </t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application\ufffeversion' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/? name=Score%20Board' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application\ufffeconfiguration' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect?to=https://github.com/juice-shop/juice-shop', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect? to=https://github.com/juice-shop/juice-shop' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'Access-Control-Allow-Origin: *', 'output': "Vulnerability has been detected on URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json' To confirm the presence of the vulnerability, this proof has been identified in the target response: | Access-Control-Allow-Origin: * The information used to check the vulnerability have been provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>['CWE 16', 'WASC Application Misconfiguration', 'OWASP 2021-A5, 2017-A6, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[""Unless the target application is specifically designed to serve public content to any domain, the 'Access-Control-Allow-Origin' should be configured with an allowlist including only known and trusted domains to perform cross-domain requests if needed, or should be disabled.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1824,7 +1827,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1841,43 +1849,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>['Configure your web server to include an `X-Frame-Options` header.']</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>['CWE 1021', 'CWE 346', 'WASC Application Misconfiguration', 'OWASP 2021-A7', 'OWASP 2017-A6', 'OWASP 2021-A4', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:N/VI:L/VA:N/SC:L/SI:L/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:N/I:L/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:N/I:P/A:N']</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
         <v>98060</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:N/VI:L/VA:N/SC:L/SI:L/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:N/I:L/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:N/I:P/A:N']</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2024-03-25T00:00:00+00:00",
@@ -1887,21 +1893,19 @@
 </t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO has no X\ufffeFrame-Options header defined', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}]</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>['CWE 1021, 346', 'WASC Application Misconfiguration', 'OWASP 2021-A7, 2017-A6, 2021-A4, 2013-A5, 2010-A6, 2023-API8, 2019-API7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>['Configure your web server to include an `X-Frame-Options` header.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1911,7 +1915,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1928,43 +1937,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>['The initial step to remedy this would be to determine whether any client-side scripts (such as JavaScript) need to access the cookie and if not, set the HttpOnly flag.', 'It should be noted that some older browsers are not compatible with the HttpOnly flag; therefore, setting this flag will not protect those clients against this form of attack.']</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>['CWE 1004', 'WASC Application Misconfiguration', 'OWASP 2010-A9', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A5']</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
         <v>98063</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2023-12-11T00:00:00+00:00",
@@ -1974,21 +1981,19 @@
 </t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'cookieconsent_status', 'payload': '', 'proof': 'cookieconsent_status=dismiss; Path=/; Expires=2026-04-25 23:10:31 +0000', 'output': "The scanner detected a cookie named 'cookieconsent_status' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'language', 'payload': '', 'proof': 'language=en; Path=/; Expires=2026-04-25 23:10:11 +0000', 'output': "The scanner detected a cookie named 'language' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'continueCode', 'payload': '', 'proof': 'continueCode=z67RBJkpxgOw1qjLrbzDM95EnABVfXDUb9A3Y2aePl4VXZvQ8mW7yKo6NXeE; Path=/; Expires=2026-04-25 23:16:47 +0000', 'output': "The scanner detected a cookie named 'continueCode' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'welcomebanner_status', 'payload': '', 'proof': 'welcomebanner_status=dismiss; Path=/; Expires=2026-04-25 23:13:45 +0000', 'output': "The scanner detected a cookie named 'welcomebanner_status' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['CWE 1004', 'WASC Application Misconfiguration', 'OWASP 2010-A9, 2013-A6, 2017-A3, 2021-A5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>['The initial step to remedy this would be to determine whether any client-side scripts (such as JavaScript) need to access the cookie and if not, set the HttpOnly flag.', 'It should be noted that some older browsers are not compatible with the HttpOnly flag; therefore, setting this flag will not protect those clients against this form of attack.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1998,7 +2003,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2015,43 +2025,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>['If the cookie contains sensitive information, then the server should ensure that the cookie has the `secure` flag set.']</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>['CWE 614', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A5']</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
         <v>98064</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2023-12-11T00:00:00+00:00",
@@ -2061,31 +2069,34 @@
 </t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'continueCode', 'payload': '', 'proof': 'continueCode=z67RBJkpxgOw1qjLrbzDM95EnABVfXDUb9A3Y2aePl4VXZvQ8mW7yKo6NXeE; Path=/; Expires=2026-04-25 23:16:47 +0000', 'output': "The scanner detected a cookie named 'continueCode' set with JavaScript without the Secure flag set.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'cookieconsent_status', 'payload': '', 'proof': 'cookieconsent_status=dismiss; Path=/; Expires=2026-04-25 23:10:31 +0000', 'output': "The scanner detected a cookie named 'cookieconsent_status' set with JavaScript without the Secure flag set.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'welcomebanner_status', 'payload': '', 'proof': 'welcomebanner_status=dismiss; Path=/; Expires=2026-04-25 23:13:45 +0000', 'output': "The scanner detected a cookie named 'welcomebanner_status' set with JavaScript without the Secure flag set.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'language', 'payload': '', 'proof': 'language=en; Path=/; Expires=2026-04-25 23:10:11 +0000', 'output': "The scanner detected a cookie named 'language' set with JavaScript without the Secure flag set.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>['CWE 614', 'WASC Insufficient Transport Layer Protection', 'OWASP 2010-A9, 2013-A6, 2017-A3, 2021-A5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>['If the cookie contains sensitive information, then the server should ensure that the cookie has the `secure` flag set.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'continueCode', 'payload': None, 'proof': 'continueCode=z67RBJkpxgOw1qjLrbzDM95EnABVfXDUb9A3Y2aePl4VXZvQ8mW7yKo6NXeE; Path=/; Expires=2026-04-25 23:16:47 +0000', 'output': "The scanner detected a cookie named 'continueCode' set with JavaScript without the Secure flag set.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'cookieconsent_status', 'payload': None, 'proof': 'cookieconsent_status=dismiss; Path=/; Expires=2026-04-25 23:10:31 +0000', 'output': "The scanner detected a cookie named 'cookieconsent_status' set with JavaScript without the Secure flag set.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'welcomebanner_status', 'payload': None, 'proof': 'welcomebanner_status=dismiss; Path=/; Expires=2026-04-25 23:13:45 +0000', 'output': "The scanner detected a cookie named 'welcomebanner_status' set with JavaScript without the Secure flag set.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'language', 'payload': None, 'proof': 'language=en; Path=/; Expires=2026-04-25 23:10:11 +0000', 'output': "The scanner detected a cookie named 'language' set with JavaScript without the Secure flag set.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2102,43 +2113,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>['Modify the HTTP headers of the web server to not disclose detailed information about the underlying web server.']</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>['CWE 200', 'WASC Information Leakage', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
         <v>98618</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2019-06-12T00:00:00+00:00",
 "modification_date": "2024-03-25T00:00:00+00:00",
@@ -2148,21 +2157,19 @@
 </t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/fr_FR.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/api/Feedbacks/: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/de_DE.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/az_AZ.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/admin/application-configuration: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/en.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/products/search?q=: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/et_EE.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/continue-code: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/cs_CZ.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/admin/application-version: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/products/1/reviews: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/id_ID.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/api/Challenges/?name=Score%20Board: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/da_DK.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/languages: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/es_ES.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/user/whoami: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/captcha/: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/api/Quantitys/: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/ftp/legal.md: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/assets/i18n/ca_ES.json: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-16-0-1-178712031365.us-west1.run. app/rest/memories/: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>['CWE 200', 'WASC Information Leakage', 'OWASP 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>['Modify the HTTP headers of the web server to not disclose detailed information about the underlying web server.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2172,7 +2179,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2189,43 +2201,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>[""Configure your web server to include an 'X-Content-Type-Options' header with a value of 'nosniff'.""]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>['CWE 693', 'WASC Application Misconfiguration', 'OWASP 2017-A6', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:L/SI:L/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
         <v>112529</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:L/SI:L/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>{"publication_date": "2018-11-28T00:00:00+00:00",
 "modification_date": "2024-03-25T00:00:00+00:00",
@@ -2234,21 +2244,19 @@
 "plugin_id": 112529}</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}]</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>['CWE 693', 'WASC Application Misconfiguration', 'OWASP 2017-A6, 2013-A5, 2010-A6, 2023-API8, 2019-API7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>[""Configure your web server to include an 'X-Content-Type-Options' header with a value of 'nosniff'.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2258,7 +2266,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2275,43 +2288,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>['Reconfigure the affected application, if possible to avoid the use of weak ciphers.']</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>['CWE 326', 'WASC Application Misconfiguration', 'OWASP 2010-A7', 'OWASP 2013-A6', 'OWASP 2017-A3', 'OWASP 2021-A2', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.3', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:P/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.7', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
         <v>112539</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>['2.3', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:P/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.7', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>{"publication_date": "2019-01-21T00:00:00+00:00",
 "modification_date": "2022-10-07T00:00:00+00:00",
@@ -2320,21 +2331,19 @@
 "plugin_id": 112539}</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength ------------------------------------------------------------------------- TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>['CWE 326', 'WASC Application Misconfiguration', 'OWASP 2010-A7, 2013-A6, 2017-A3, 2021-A2, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>['Reconfigure the affected application, if possible to avoid the use of weak ciphers.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2344,7 +2353,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2361,43 +2375,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>[""Configure Content Security Policy on your website by adding 'Content-Security-Policy' HTTP header or meta tag http-equiv='Content-Security-Policy'.""]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>['CWE 1021', 'WASC Application Misconfiguration', 'OWASP 2017-A6', 'OWASP 2021-A4', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
         <v>112551</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2019-02-14T00:00:00+00:00",
 "modification_date": "2024-03-25T00:00:00+00:00",
@@ -2407,21 +2419,19 @@
 </t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders has no Content Security Policy defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/coupons_2013.md.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/coupons_2013.md.bak has no Content Security Policy defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/public/images/uploads/%F0%9F%98%BC\ufffeIdentification', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/public/images/uploads/%F0%9F%98%BC- has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>['CWE 1021', 'WASC Application Misconfiguration', 'OWASP 2017-A6, 2021-A4, 2013-A5, 2010-A6, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>[""Configure Content Security Policy on your website by adding 'Content-Security-Policy' HTTP header or meta tag http-equiv='Content-Security-Policy'.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2431,7 +2441,12 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2448,43 +2463,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>[""Configure your web server to include a 'Cache-Control' header with appropriate directives. If page contains sensitive information 'Cache-Control' value should be 'no-store' and 'Pragma' header value should be 'no-cache'.""]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>['CWE 525', 'WASC Application Misconfiguration', 'OWASP 2017-A6', 'OWASP 2021-A4', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.7', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
         <v>112553</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.7', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">{"publication_date": "2019-02-15T00:00:00+00:00",
 "modification_date": "2024-03-25T00:00:00+00:00",
@@ -2494,21 +2507,19 @@
 </t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q= has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/quarantine/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/coupons_2013.md.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/coupons_2013.md.bak has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>['CWE 525', 'WASC Application Misconfiguration', 'OWASP 2017-A6, 2021-A4, 2013-A5, 2010-A6, 2023-API8, 2019-API7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>[""Configure your web server to include a 'Cache-Control' header with appropriate directives. If page contains sensitive information 'Cache-Control' value should be 'no-store' and 'Pragma' header value should be 'no-cache'.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2518,7 +2529,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2535,43 +2551,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>['Avoid disclosing usernames in your application content.']</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>['CWE 16', 'CWE 200', 'WASC Application Misconfiguration', 'WASC Information Leakage', 'OWASP 2021-A5', 'OWASP 2017-A6', 'OWASP 2021-A1', 'OWASP 2013-A5', 'OWASP 2010-A6', 'OWASP 2023-API8', 'OWASP 2023-API3', 'OWASP 2019-API3', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.3', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:P/PR:N/UI:P/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.7', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
         <v>114615</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>['2.3', 'CVSS:4.0/AV:N/AC:H/AT:P/PR:N/UI:P/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.7', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:N/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>{"publication_date": "2025-03-11T00:00:00+00:00",
 "modification_date": "2025-03-11T00:00:00+00:00",
@@ -2580,21 +2594,19 @@
 "plugin_id": 114615}</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - "user":"bjoernGoogle"', 'output': 'The scanner identified one or more `Generic` username(s) on the target page.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - "username":"bkimminich" - "username":"evmrox"', 'output': 'The scanner identified one or more `Generic` username(s) on the target page.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - "user":"bjoernGoogle"', 'output': 'The scanner identified one or more `Generic` username(s) on the target page.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>['CWE 16, 200', 'WASC Application Misconfiguration, Information Leakage', 'OWASP 2021-A5, 2017-A6, 2021-A1, 2013-A5, 2010-A6, 2023-API8, 2023-API3, 2019-API3, 2019-API7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>['Avoid disclosing usernames in your application content.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2604,7 +2616,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2621,43 +2638,41 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>[""Web browsers default behavior may differ when processing cookies in a cross-site context, making the final decision to send the cookie in this context unpredictable. The SameSite attribute should be set in every cookie to enforce the expected result by developers. When using the 'None' attribute value, ensure that the cookie is also set with the 'Secure' flag.""]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>['CWE 352', 'WASC Cross-Site Request Forgery', 'OWASP 2013-A8', 'OWASP 2010-A5', 'OWASP 2021-A1', 'OWASP 2023-API8', 'OWASP 2019-API7']</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>['CVSSV4 BASE SCORE 2.1', 'CVSSV4 VECTOR CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', 'CVSSV3 BASE SCORE 3.1', 'CVSSV3 VECTOR CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', 'CVSS BASE SCORE 2.6', 'CVSS VECTOR CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
         <v>115540</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>['2.1', 'CVSS:4.0/AV:N/AC:H/AT:N/PR:N/UI:A/VC:L/VI:N/VA:N/SC:N/SI:N/SA:N', '3.1', 'CVSS:3.0/AV:N/AC:H/PR:N/UI:R/S:U/C:L/I:N/A:N', '2.6', 'CVSS2#AV:N/AC:H/Au:N/C:P/I:N/A:N']</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>{"publication_date": "2018-12-14T00:00:00+00:00",
 "modification_date": "2023-12-11T00:00:00+00:00",
@@ -2666,21 +2681,19 @@
 "plugin_id": 115540}</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'cookieconsent_status', 'payload': '', 'proof': 'cookieconsent_status=dismiss; Path=/; Expires=2026-04-25 23:10:31 +0000', 'output': "The scanner detected a cookie named 'cookieconsent_status' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'continueCode', 'payload': '', 'proof': 'continueCode=z67RBJkpxgOw1qjLrbzDM95EnABVfXDUb9A3Y2aePl4VXZvQ8mW7yKo6NXeE; Path=/; Expires=2026-04-25 23:16:47 +0000', 'output': "The scanner detected a cookie named 'continueCode' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'welcomebanner_status', 'payload': '', 'proof': 'welcomebanner_status=dismiss; Path=/; Expires=2026-04-25 23:13:45 +0000', 'output': "The scanner detected a cookie named 'welcomebanner_status' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'language', 'payload': '', 'proof': 'language=en; Path=/; Expires=2026-04-25 23:10:11 +0000', 'output': "The scanner detected a cookie named 'language' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>['CWE 352', 'WASC Cross-Site Request Forgery', 'OWASP 2013-A8, 2010-A5, 2021-A1, 2023-API8, 2019-API7', 'CVE -', 'BID -']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>[""Web browsers default behavior may differ when processing cookies in a cross-site context, making the final decision to send the cookie in this context unpredictable. The SameSite attribute should be set in every cookie to enforce the expected result by developers. When using the 'None' attribute value, ensure that the cookie is also set with the 'Secure' flag.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2690,7 +2703,12 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2707,43 +2725,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
         <v>98000</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "023-11-17T00:00:00+00:00",
@@ -2752,13 +2764,11 @@
 "plugin_id": 98000}</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "Engine Version 2.32.4-1790 Plugins Version 202504170639 Scan ID 98147a45-d7d1-4fb3-a532-d4d4b2db551e Start Time 2025-04-25 23:10:05 +0000 Duration 09:02:14 Requests 541973 Crawler Requests 98 Requests/s 20.8353 Mean Response Time 0.1956s Bandwidth Usage - Data to Target 356 MB - Data from Target 6.4 GB Timeouts Encountered Network Timeouts 3 Browser Timeouts 0 Browser Respawns 0 HTTP Protocols Detected - HTTPs Authentication Identified - None Plugins - 811 have been included per scan policy - 612 have been started based on target information collected List of plugins is available in 'plugins.csv' attachment. Settings used to conduct this scan are available in 'configuration.csv' attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2776,7 +2786,12 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2810,45 +2825,35 @@
 user_abort: The user stopped the scan before the URL could be audited']</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
         <v>98009</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2023-11-17T00:00:00+00:00",
@@ -2857,19 +2862,21 @@
 "plugin_id": 98009}</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scan has discovered 5122 distinct URLs. The following is a breakdown of which URLs were audited: - 43 effectively audited - 5 not audited due to the page was too similar to another page already audited - 1 not audited due to not being within the bounds of the user defined scan scope - 4973 not queued due to the URL being considered redundant with other processed URLs - 49 not queued due to file extension exclusions - 31 not queued due to the URL not being in the target domain - 17 not queued due to the URL containing a fragment which is a feature of browsers and not included in HTTP requests. The page being referred to by the fragment shall still be audited by the scanner. For URLs we received responses for, here is a distribution of the content type headers: - 126 application/json - 24 application/json; charset=utf-8 - 5 application/octet-stream - 36 image/jpeg - 6 image/png - 2 text/css; charset=utf-8 - 1454 text/html - 24 text/html; charset=utf-8 - 3 text/markdown; charset=utf-8 - 3400 text/plain; charset=utf-8 Response times ranged between 0.061378s and 0.281365s. You can access the complete list of URLs with the information collected by the scan as an attachment to this plugin.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2877,7 +2884,12 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2894,43 +2906,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>['Check your web application logs and verify that it is functioning as expected and can handle significant amounts of traffic generated by the scanner.', 'Additionally, the scan policy may be edited to optimize the performance settings.']</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
         <v>98019</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-09-25T00:00:00+00:00",
 "modification_date": "2023-11-17T00:00:00+00:00",
@@ -2939,13 +2945,11 @@
 "plugin_id": 98019}</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner encountered 3 network timeouts during the scan. See the attachment for more details', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2953,7 +2957,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>['Check your web application logs and verify that it is functioning as expected and can handle significant amounts of traffic generated by the scanner.', 'Additionally, the scan policy may be edited to optimize the performance settings.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2963,7 +2967,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2980,43 +2989,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>['It is recommended that a whitelisting approach be taken to explicitly permit only the HTTP methods required by the application and block all others.']</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
         <v>98047</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2024-02-27T00:00:00+00:00",
@@ -3025,13 +3028,11 @@
 "plugin_id": 98047}</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify several HTTP methods that can be used for one or several URLs. The results are available as attachments.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3039,7 +3040,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>['It is recommended that a whitelisting approach be taken to explicitly permit only the HTTP methods required by the application and block all others.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3049,7 +3050,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3066,43 +3072,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
         <v>98050</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2021-06-14T00:00:00+00:00",
@@ -3111,13 +3111,11 @@
 "plugin_id": 98050}</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 405', 'output': "A response has been received with a response code '405' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP TRACE request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/'.", 'request_method': 'TRACE', 'http_status_code': 405, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/content/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP POST request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/api/content/'.", 'request_method': 'POST', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/?wsdl', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/?wsdl'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v1/swagger.yaml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v1/swagger.yaml'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/v2/swagger.yaml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/v2/swagger.yaml'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/swagger.yaml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/swagger.yaml'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/login', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP POST request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/api/login'.", 'request_method': 'POST', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v2/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v2/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https%3A%2F%2Fjuice-shop-16-0-1-178712031365.us-west1.run.app%2Fsetup%2Fsetup-s%2F%25u002e%25u002e%2F%', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 400', 'output': "A response has been received with a response code '400' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/setup/setup-s/%u002e%u002e/%u002e%u002e/log.jsp'.", 'request_method': 'GET', 'http_status_code': 400, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v1/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v1/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/was-tnb.aspx', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 502', 'output': "A response has been received with a response code '502' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP DEBUG request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/was-tnb.aspx'.", 'request_method': 'DEBUG', 'http_status_code': 502, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/v2/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/v2/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/api-docs/'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/profile/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/profile/'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/cors/https/rfi.nessus.org/rfi.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/cors/https/rfi.nessus.org/rfi.txt'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect?to=1%29%7Bwindow.top.', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/1.1 406 Not Acceptable', 'output': "A response has been received with a response code '406' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/redirect?to=1%29%7Bwindow.top._tenable_wasscan_js_namespace_taint_tracer.log_execution_flow_sink%28%29%2F%2F'.", 'request_method': '', 'http_status_code': 406, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v1/status/config', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v1/status/config'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/restricted/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/restricted/'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/components/suggestions?recentlyBrowsed=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/components/suggestions?recentlyBrowsed='.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/wls-wsat/CoordinatorPortType', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 413', 'output': "A response has been received with a response code '413' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP POST request made on the URL 'https://juice-shop-16-0-1-178712031365.us\ufffewest1.run.app/wls-wsat/CoordinatorPortType'.", 'request_method': 'POST', 'http_status_code': 413, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/v1/swagger.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/v1/swagger.json'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/v1/targets', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/v1/targets'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/docs/v1/swagger.yaml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 500', 'output': "A response has been received with a response code '500' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-16-0-1-178712031365.us-west1. run.app/api/docs/v1/swagger.yaml'.", 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3135,7 +3133,12 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3152,43 +3155,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>['Only use components that do not have known vulnerabilities, only use components that when combined to not introduce a security vulnerability, and ensure that a misconfiguration does not cause any vulnerabilities']</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
         <v>98059</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-12-06T00:00:00+00:00",
 "modification_date": "2023-11-17T00:00:00+00:00",
@@ -3197,13 +3194,11 @@
 "plugin_id": 98059}</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The framework has detected the following technologies in the target application: - jQuery (v2.2.4) - Swagger UI (version unknown)', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3211,7 +3206,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>['Only use components that do not have known vulnerabilities, only use components that when combined to not introduce a security vulnerability, and ensure that a misconfiguration does not cause any vulnerabilities']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3221,7 +3216,12 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3238,43 +3238,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
         <v>98061</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>{"publication_date": "2020-09-01T00:00:00+00:00",
 "modification_date": "2023-11-17T00:00:00+00:00",
@@ -3283,13 +3277,11 @@
 "plugin_id": 98061}</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following cookies have been collected during the scan of the target: - 0 cookie(s) specified via Set-Cookie - 10 cookie(s) set via JavaScript code The complete list of the cookies is available in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3307,7 +3299,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3324,43 +3321,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>['If directories are unreferenced, then they should be removed from the web root and/or the application directory.', 'Preventing access without authentication may also be an option and can stop a client from being able to view the contents of a file; however, it is still likely that the directory structure will be able to be discovered.', ""Using obscure directory names is implementing 'security through obscurity' and is not a recommended option.""]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
         <v>98072</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2024-01-03T00:00:00+00:00",
@@ -3369,13 +3360,11 @@
 "plugin_id": 98072}</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'search' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'api-docs' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'ftp' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'reviews' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3383,17 +3372,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>['If directories are unreferenced, then they should be removed from the web root and/or the application directory.', 'Preventing access without authentication may also be an option and can stop a client from being able to view the contents of a file; however, it is still likely that the directory structure will be able to be discovered.', ""Using obscure directory names is implementing 'security through obscurity' and is not a recommended option.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search/', 'input_type': None, 'input_name': None, 'payload': None, 'proof': None, 'output': "The common directory 'search' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': None, 'input_name': None, 'payload': None, 'proof': None, 'output': "The common directory 'api-docs' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/', 'input_type': None, 'input_name': None, 'payload': None, 'proof': None, 'output': "The common directory 'ftp' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews/', 'input_type': None, 'input_name': None, 'payload': None, 'proof': None, 'output': "The common directory 'reviews' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3410,43 +3404,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>['Identifying the context in which the affected page displays a Private IP address is necessary.', 'If the page is publicly accessible and displays the Private IP of the affected server (or supporting infrastructure), then measures should be put in place to ensure that the IP address is removed from any response.']</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
         <v>98077</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2024-12-03T00:00:00+00:00",
@@ -3455,13 +3443,11 @@
 "plugin_id": 98077}</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Number of Private IP Addresses Collected: 4 Listed below are each private ip address: 127.0.0.1 found on 1 URL 192.168.99.100 found on 1 URL 169.254.169.254 found on 1 URL 169.254.169.126 found on 1 URL', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3469,7 +3455,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>['Identifying the context in which the affected page displays a Private IP address is necessary.', 'If the page is publicly accessible and displays the Private IP of the affected server (or supporting infrastructure), then measures should be put in place to ensure that the IP address is removed from any response.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3479,7 +3465,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3496,43 +3487,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>['E-mail addresses should be presented in such a way that it is hard to process them automatically.']</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
         <v>98078</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-03-31T00:00:00+00:00",
 "modification_date": "2023-11-17T00:00:00+00:00",
@@ -3541,13 +3526,11 @@
 "plugin_id": 98078}</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Number of Email Addresses Collected: 10 Listed below are each email address and the number of URLs where the email address has been found: donotreply@owasp-juice.shop found on 1 URL admin@juice-sh.op found on 3 URLs ethereum@juice-sh.op found on 1 URL john@juice-sh.op found on 1 URL emma@juice-sh.op found on 1 URL in@juice-sh.op found on 2 URLs der@juice-sh.op found on 2 URLs ereum@juice-sh.op found on 2 URLs bjoern@owasp.org found on 1 URL bjoern.kimminich@gmail.com found on 1 URL', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3555,7 +3538,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>['E-mail addresses should be presented in such a way that it is hard to process them automatically.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3565,7 +3548,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3582,43 +3570,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
         <v>98136</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>{"publication_date": "2017-07-27T00:00:00+00:00",
 "modification_date": "2024-04-26T00:00:00+00:00",
@@ -3627,13 +3609,11 @@
 "plugin_id": 98136}</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "Access to URL 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/' has been confirmed. Target Information ------------------------ Domain Name : juice-shop-16-0-1-178712031365.us-west1.run.app IP Address : 216.239.32.53 Response Information --------------------------- Status Code : 200 Return Code : ok Return Message: No error Response Time : 0.137635s Response Size : 4247 bytes Content-Type : text/html; charset=UTF-8 DEBUG INFORMATION ----------------------- HTTP Network Timeout : 30s", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3651,7 +3631,12 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3668,43 +3653,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
         <v>98138</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>{"publication_date": "2018-01-23T00:00:00+00:00",
 "modification_date": "2018-02-14T00:00:00+00:00",
@@ -3713,13 +3692,11 @@
 "plugin_id": 98138}</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "WAS Scanner has taken a screenshot of the page at url 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/' with dimensions 1600x1200. Please see the attachment for the screenshot image.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3737,7 +3714,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3754,43 +3736,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
         <v>98148</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>{"publication_date": "2021-10-21T00:00:00+00:00",
 "modification_date": "2021-10-21T00:00:00+00:00",
@@ -3799,13 +3775,11 @@
 "plugin_id": 98148}</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2/orders', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app /b2b/v2/orders with no input fields This form is submitted by using the following action : https://juice-shop-16-0-1-178712031365.us-west1.run.app/b2b/v2 /orders', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': 'form', 'input_name': 'combined:get::https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app /api-docs/ with input fields : - download-url-input (text) This form is submitted by using the following action : https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app /socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpGv&amp;sid=0N98D_jaorFN-7ioAAAK with no input fields This form is submitted by using the following action : https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket. io/?EIO=4&amp;transport=polling&amp;t=PPlDpGv&amp;sid=0N98D_jaorFN-7ioAAAK', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?', 'input_type': 'form', 'input_name': 'combined:get::https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-16-0-1-178712031365.us-west1.run.app /socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpGv&amp;sid=0N98D_jaorFN-7ioAAAK with no input fields This form is submitted by using the following action : https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket. io/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3823,7 +3797,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3840,43 +3819,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
         <v>98154</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>{"publication_date": "2022-11-30T00:00:00+00:00",
 "modification_date": "2022-12-12T00:00:00+00:00",
@@ -3885,13 +3858,11 @@
 "plugin_id":98154 }</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the presence of 30 URLs on the target application: - 0 URLs which use a hostname related to the target hostname - 30 URLs which use a third party hostname The list of the detected URLs is provided in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3909,7 +3880,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3926,43 +3902,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>[""Configure Permissions Policy on your website by adding 'Permissions-Policy' HTTP header.""]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
         <v>98526</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>{"publication_date": "2019-03-27T00:00:00+00:00",
 "modification_date": "2024-03-25T00:00:00+00:00",
@@ -3971,13 +3941,11 @@
 "plugin_id": 98526}</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score% 20Board but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/? EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application\ufffeconfiguration but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application\ufffeversion but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q= but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A Feature-Policy header was found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/ but this header must be renamed to Permissions-Policy.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3985,7 +3953,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>[""Configure Permissions Policy on your website by adding 'Permissions-Policy' HTTP header.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3995,7 +3963,12 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4012,43 +3985,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>[""Configure Referrer Policy on your website by adding 'Referrer-Policy' HTTP header or meta tag referrer in HTML.""]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
         <v>98527</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>{"publication_date": "2019-04-02T00:00:00+00:00",
 "modification_date": "2024-03-25T00:00:00+00:00",
@@ -4057,13 +4024,11 @@
 "plugin_id": 98527}</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-configuration', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /admin/application-configuration', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/de_DE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/de_DE.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp/legal.md', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/ftp /legal.md', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/markdown'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/1/reviews', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /products/1/reviews', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/continue-code', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /continue-code', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/user/whoami', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /user/whoami', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/products/search?q=', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /products/search?q=', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/ca_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/ca_ES.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/es_ES.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/es_ES.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/captcha/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /captcha/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/cs_CZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/cs_CZ.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api /Feedbacks/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/en.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/en.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/da_DK.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/da_DK.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/languages', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /languages', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /socket.io/?EIO=4&amp;transport=polling&amp;t=PPlDpDO', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'text/plain'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/et_EE.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/et_EE.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/az_AZ.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/az_AZ.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api /Quantitys/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/?name=Score%20Board', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/api /Challenges/?name=Score%20Board', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/memories/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /memories/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/id_ID.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/id_ID.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/i18n/fr_FR.json', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app /assets/i18n/fr_FR.json', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest/admin/application-version', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-16-0-1-178712031365.us-west1.run.app/rest /admin/application-version', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4071,7 +4036,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>[""Configure Referrer Policy on your website by adding 'Referrer-Policy' HTTP header or meta tag referrer in HTML.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4081,7 +4046,12 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4098,43 +4068,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>['Add a integrity attribute to the resource tag with prefixed and base64 encoded hash of the resource.']</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
         <v>98647</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>{"publication_date": "2019-08-01T00:00:00+00:00",
 "modification_date": "2023-01-17T00:00:00+00:00",
@@ -4143,13 +4107,11 @@
 "plugin_id": 98647}</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The scanner detected 4 resources without subresource integrity defined : - 2 URLs related to 'script' resources - 2 URLs related to 'link' resources The list of all the detected resources is provided in attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4157,7 +4119,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>['Add a integrity attribute to the resource tag with prefixed and base64 encoded hash of the resource.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4167,7 +4129,12 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4184,43 +4151,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>[""Review the contents of the site's robots.txt file, use Robots META tags instead of entries in the robots.txt file, and/or adjust the web server's access controls to limit access to sensitive material.""]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
         <v>98705</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>{"publication_date": "2019-09-19T00:00:00+00:00",
 "modification_date": "2020-12-17T00:00:00+00:00",
@@ -4229,13 +4190,11 @@
 "plugin_id": 98705}</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/robots.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "A robots.txt file was detected at 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/robots.txt'.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4243,17 +4202,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>[""Review the contents of the site's robots.txt file, use Robots META tags instead of entries in the robots.txt file, and/or adjust the web server's access controls to limit access to sensitive material.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/robots.txt', 'input_type': None, 'input_name': None, 'payload': None, 'proof': None, 'output': "A robots.txt file was detected at 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/robots.txt'.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4270,43 +4234,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
         <v>98772</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>{"publication_date": "2019-11-14T00:00:00+00:00",
 "modification_date": "2023-11-17T00:00:00+00:00",
@@ -4315,13 +4273,11 @@
 "plugin_id": 98772}</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scan detected 7631 unique XMLHttpRequests. Here is the distribution of MIME types used by the detected requests: - 174 as "application/json" - 5045 as "text/plain" - 2284 as "text/html" - 5 as "application/octet-stream" - 123 with no specified or detected MIME type The scan detected 15 unique Fetch Requests. Here is the distribution of MIME types used by the detected requests: - 5 as "application/json" - 7 as "text/html" - 1 as "text/fragment+html" - 1 as "text/plain" - 1 with no specified or detected MIME type', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4339,7 +4295,12 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4356,43 +4317,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
         <v>112491</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>{"publication_date": "2018-10-03T00:00:00+00:00",
 "modification_date": "2023-05-05T00:00:00+00:00",
@@ -4401,13 +4356,11 @@
 "plugin_id": 112491}</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Certificate 1 -------------- Common Name: *.a.run.app Alternative Names: *.a.run.app run.app *.africa-south1.run.app *.asia-east1.run.app *.asia-east2.run.app *.asia\ufffenortheast1.run.app *.asia-northeast2.run.app *.asia-northeast3.run.app *.asia-south1.run.app *.asia-south2.run.app *. asia-southeast1.run.app *.asia-southeast2.run.app *.asia-southeast3.run.app *.australia-southeast1.run.app *.australia\ufffesoutheast2.run.app *.europe-central2.run.app *.europe-north1.run.app *.europe-north2.run.app *.europe-southwest1.run. app *.europe-west1.run.app *.europe-west10.run.app *.europe-west12.run.app *.europe-west15.run.app *.europe-west2.run. app *.europe-west3.run.app *.europe-west4.run.app *.europe-west5.run.app *.europe-west6.run.app *.europe-west8.run.app *.europe-west9.run.app *.me-central1.run.app *.me-central2.run.app *.me-west1.run.app *.northamerica-northeast1.run.app *.northamerica-northeast2.run.app *.northamerica-south1.run.app *.southamerica-east1.run.app *.southamerica-west1.run. app *.us-central1.run.app *.us-central2.run.app *.us-east1.run.app *.us-east4.run.app *.us-east5.run.app *.us-east7.run. app *.us-south1.run.app *.us-west1.run.app *.us-west2.run.app *.us-west3.run.app *.us-west4.run.app *.us-west8.run.app Issuer: Google Trust Services Valid from: 2025-03-31 08:54:20 UTC Valid until: 2025-06-23 08:54:19 UTC (expires in 1 month, 3 weeks, 6 days) Validity Period: 83 days Key: 256-bit Signature: ecdsa-with-SHA256 Certificate 2 -------------- Common Name: we2 Issuer: Google Trust Services LLC Valid from: 2023-12-13 09:00:00 UTC Valid until: 2029-02-20 14:00:00 UTC (expires in 3 years, 9 months, 3 weeks, 5 days) Validity Period: 1896 days Key: 256-bit Signature: ecdsa-with-SHA384 Certificate 3 -------------- Common Name: gts root r4 Issuer: GlobalSign nv Valid from: 2023-11-15 03:43:21 UTC Valid until: 2028-01-28 00:00:42 UTC (expires in 2 years, 9 months, 2 days) Validity Period: 1534 days Key: RSA 384-bit Signature: sha256WithRSAEncryption', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4425,7 +4378,12 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4442,43 +4400,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
         <v>112530</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>{"publication_date": "2018-10-03T00:00:00+00:00",
 "modification_date": "2020-10-02T00:00:00+00:00",
@@ -4487,13 +4439,11 @@
 "plugin_id": 112530}</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Supported --------------------- SSL 2.0 No SSL 3.0 No TLS 1.0 No TLS 1.1 No TLS 1.2 Yes TLS 1.3 Yes', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4511,7 +4461,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4528,43 +4483,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>['Disable all notice, warning and error displaying.']</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
         <v>112550</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>{"publication_date": "2018-12-13T00:00:00+00:00",
 "modification_date": "2024-10-03T00:00:00+00:00",
@@ -4573,13 +4522,11 @@
 "plugin_id": 112550}</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - C:\\\\Windows\\\\system', 'output': 'The scanner detected the disclosure of full paths in the web application response.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/json'}]</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4587,7 +4534,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>['Disable all notice, warning and error displaying.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4597,7 +4544,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4614,43 +4566,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
         <v>112599</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>{"publication_date": "2020-09-24T00:00:00+00:00",
 "modification_date": "2021-08-25T00:00:00+00:00",
@@ -4659,13 +4605,11 @@
 "plugin_id": 112599}</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected that the remote host is not configured with a cipher suite preference for the following protocol (s) : TLS v1.2, TLS v1.3', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4683,7 +4627,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4700,43 +4649,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
         <v>112613</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>{"publication_date": "2020-10-13T00:00:00+00:00",
 "modification_date": "2023-01-17T00:00:00+00:00",
@@ -4745,13 +4688,11 @@
 "plugin_id": 112613}</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the following HTTP versions on the target application : - HTTP/1.0 - HTTP/1.1 - HTTP/2 The list of requests and responses observed is provided in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4769,7 +4710,12 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4786,43 +4732,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
         <v>112615</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>{"publication_date": "2020-10-20T00:00:00+00:00",
 "modification_date": "2024-01-08T00:00:00+00:00",
@@ -4831,13 +4771,11 @@
 "plugin_id": 112615}</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to detect a Swagger or OpenAPI definition file on https://juice-shop-16-0-1-178712031365.us-west1. run.app/api-docs/. The file is available in attachments.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4855,7 +4793,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4872,43 +4815,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
         <v>112616</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>{"publication_date": "2020-10-21T00:00:00+00:00",
 "modification_date": "2020-10-21T00:00:00+00:00",
@@ -4917,13 +4854,11 @@
 "plugin_id": 112616}</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'API endpoints have been detected for the following host(s): - https://juice-shop-16-0-1-178712031365.us-west1.run.app - https://github.com', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4941,7 +4876,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4958,43 +4898,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
         <v>112722</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>{"publication_date": "2021-03-17T00:00:00+00:00",
 "modification_date": "2022-04-29T00:00:00+00:00",
@@ -5003,13 +4937,11 @@
 "plugin_id": 112722}</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/.well-known/security.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "A security.txt file was detected at 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/.well-known/security.txt'.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5022,12 +4954,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/.well-known/security.txt', 'input_type': None, 'input_name': None, 'payload': None, 'proof': None, 'output': "A security.txt file was detected at 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/.well-known/security.txt'.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5044,43 +4981,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>['Upgrade to the latest version of JQuery.']</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
         <v>113027</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>{"publication_date": "2021-10-25T00:00:00+00:00",
 "modification_date": "2024-01-11T00:00:00+00:00",
@@ -5089,13 +5020,11 @@
 "plugin_id": 113027}</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology jQuery has been detected with version 2.2.4. Latest version available is : 3.7.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5103,7 +5032,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>['Upgrade to the latest version of JQuery.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5113,7 +5042,12 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5130,43 +5064,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
         <v>113045</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>{"publication_date": "2021-11-10T00:00:00+00:00",
 "modification_date": "2021-11-10T00:00:00+00:00",
@@ -5175,13 +5103,11 @@
 "plugin_id": 113045}</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A wildcard symbol (*) has been detected in the following certificate entries: Certificate Common Name: *.a.run.app Certificate Subject Alternative Names: - *.a.run.app - *.africa-south1.run.app - *.asia-east1.run.app - *.asia-east2.run.app - *.asia-northeast1.run.app - *.asia-northeast2.run.app - *.asia-northeast3.run.app - *.asia-south1.run.app - *.asia-south2.run.app - *.asia-southeast1.run.app - *.asia-southeast2.run.app - *.asia-southeast3.run.app - *.australia-southeast1.run.app - *.australia-southeast2.run.app - *.europe-central2.run.app - *.europe-north1.run.app - *.europe-north2.run.app - *.europe-southwest1.run.app - *.europe-west1.run.app - *.europe-west10.run.app - *.europe-west12.run.app - *.europe-west15.run.app - *.europe-west2.run.app - *.europe-west3.run.app - *.europe-west4.run.app - *.europe-west5.run.app - *.europe-west6.run.app - *.europe-west8.run.app - *.europe-west9.run.app - *.me-central1.run.app - *.me-central2.run.app - *.me-west1.run.app - *.northamerica-northeast1.run.app - *.northamerica-northeast2.run.app - *.northamerica-south1.run.app - *.southamerica-east1.run.app - *.southamerica-west1.run.app - *.us-central1.run.app - *.us-central2.run.app - *.us-east1.run.app - *.us-east4.run.app - *.us-east5.run.app - *.us-east7.run.app - *.us-south1.run.app - *.us-west1.run.app - *.us-west2.run.app - *.us-west3.run.app - *.us-west4.run.app - *.us-west8.run.app', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5199,7 +5125,12 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5216,43 +5147,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
         <v>113393</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>{"publication_date": "2022-10-17T00:00:00+00:00",
 "modification_date": "2024-10-03T00:00:00+00:00",
@@ -5261,13 +5186,11 @@
 "plugin_id": 113393}</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Three attachments are included in this finding to assist in performance tuning of your scan: -pages_telemetry.csv: Scan statistics organized by page -plugins_telemetry.csv: Scan statistics organized by plugin -time_telemetry.csv: Chronological scan statistics', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5285,7 +5208,12 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5302,43 +5230,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>['Remove the message event listener if this is not needed in the application logic or verify that the message sender origin is matching with a trusted allowlist.']</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
         <v>113851</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>{"publication_date": "2023-05-05T00:00:00+00:00",
 "modification_date": "2023-05-05T00:00:00+00:00",
@@ -5347,13 +5269,11 @@
 "plugin_id": 113851}</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the presence of listeners which does not check for the message origin. The code of the JavaScript function used by the listener is available in attachment.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5361,7 +5281,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>['Remove the message event listener if this is not needed in the application logic or verify that the message sender origin is matching with a trusted allowlist.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5371,7 +5291,12 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5388,43 +5313,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>['Review the HTML comments identified on the page for any information leakage, and remove any sensitive information identified.']</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
         <v>113897</v>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>{"publication_date": "2023-06-09T00:00:00+00:00",
 "modification_date": "2024-11-08T00:00:00+00:00",
@@ -5433,13 +5352,11 @@
 "plugin_id": 113897}</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '3 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/public/images/uploads/%F0%9F%98%BCIdentification', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5447,17 +5364,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>['Review the HTML comments identified on the page for any information leakage, and remove any sensitive information identified.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': None, 'input_name': None, 'payload': None, 'proof': None, 'output': '3 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/public/images/uploads/%F0%9F%98%BC-', 'input_type': None, 'input_name': None, 'payload': None, 'proof': None, 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/1.1', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5474,43 +5396,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
         <v>114132</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>{"publication_date": "2023-12-18T00:00:00+00:00",
 "modification_date": "2023-12-18T00:00:00+00:00",
@@ -5519,13 +5435,11 @@
 "plugin_id": 114132}</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/swagger-ui-bundle.js', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to detect the presence of JavaScript source maps in the response body.The following source map files were detected : - https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/swagger-ui-bundle.js.map', 'request_method': 'GET', 'http_status_code': None, 'http_protocol': 'HTTP/2', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5543,7 +5457,12 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5560,43 +5479,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
         <v>114135</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>{"publication_date": "2023-12-18T00:00:00+00:00",
 "modification_date": "2023-12-18T00:00:00+00:00",
@@ -5605,13 +5518,11 @@
 "plugin_id": 114135}</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect', 'input_type': 'link', 'input_name': 'to', 'payload': 'was-tnb-jmx', 'proof': "Input reflected in the response body : 'was-tnb-jmx'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 406, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5624,12 +5535,17 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/redirect', 'input_type': 'link', 'input_name': 'to', 'payload': 'was-tnb-jmx', 'proof': "Input reflected in the response body : 'was-tnb-jmx'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 406, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5646,43 +5562,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
         <v>114395</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>{"publication_date": "2024-08-12T00:00:00+00:00",
 "modification_date": "2024-08-12T00:00:00+00:00",
@@ -5691,13 +5601,11 @@
 "plugin_id": 114395}</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The scanner detected a WebSocket creation to the following endpoint: wss://juice-shop-16-0-1-178712031365.us-west1.run. app/socket.io/?EIO=4&amp;transport=websocket&amp;sid=q57_qHGEncDGUU1JAABc.The WebSocket creation has been initialized by the following resource : https://juice-shop-16-0-1-178712031365.us-west1.run.app/vendor.js (script)', 'output': 'The scanner was able to identify the usage of WebSockets on the target application.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5715,7 +5623,12 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5732,43 +5645,37 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>[""It is preferable not to use path-related URLs in stylesheet imports, and also to use the 'X-Content-Type-Options: nosnif' and 'X-Frame-Options: deny' headers.""]</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
         <v>114466</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>{"publication_date": "2024-10-30T00:00:00+00:00",
 "modification_date": "2024-11-08T00:00:00+00:00",
@@ -5777,13 +5684,11 @@
 "plugin_id": 114466}</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * styles.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/assets/public/images/uploads/%F0%9F%98%BC\ufffeIdentification', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * styles.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * ./swagger-ui.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5791,7 +5696,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>[""It is preferable not to use path-related URLs in stylesheet imports, and also to use the 'X-Content-Type-Options: nosnif' and 'X-Frame-Options: deny' headers.""]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5801,7 +5706,12 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5818,43 +5728,37 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>['Review all the detected virtual hosts to ensure they are expected to be externally reachable.']</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
         <v>114503</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>{"publication_date": "2024-11-20T00:00:00+00:00",
 "modification_date": "2024-11-26T00:00:00+00:00",
@@ -5863,13 +5767,11 @@
 "plugin_id": 114503}</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "By crafting a request with a specific 'Host' header the scanner obtained a different response", 'output': "The scanner was able to detect the present of another virtual host on the target ip 216.239.32.53: 'admin.us-west1.run. app:443'", 'request_method': 'GET', 'http_status_code': 404, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5877,7 +5779,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>['Review all the detected virtual hosts to ensure they are expected to be externally reachable.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5887,7 +5789,12 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5904,43 +5811,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
         <v>114608</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>{"publication_date": "2025-03-03T00:00:00+00:00",
 "modification_date": "2025-03-03T00:00:00+00:00",
@@ -5949,13 +5850,11 @@
 "plugin_id": 114608}</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/SecurityQuestions/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Quantitys/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Challenges/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api/Feedbacks/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/api-docs/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify a REST API.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5973,7 +5872,12 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -5990,43 +5894,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>TENABLEWAS</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
         <v>115491</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>{"publication_date": "2019-01-09T00:00:00+00:00",
 "modification_date": "2022-10-07T00:00:00+00:00",
@@ -6035,13 +5933,11 @@
 "plugin_id": 115491}</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>[{'instance': 'https://juice-shop-16-0-1-178712031365.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength ---------------------------------------------------------------------------- TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_GCM_SHA256 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_CHACHA20_POLY1305 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_GCM_SHA384 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_GCM_SHA256 x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_GCM_SHA384 x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096 TLS1.3 TLS_AES_128_GCM_SHA256 x25519 256 TLS1.3 TLS_AES_256_GCM_SHA384 x25519 256 TLS1.3 TLS_CHACHA20_POLY1305_SHA256 x25519 256', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6059,7 +5955,12 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>TENABLEWAS</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
